--- a/data/trans_dic/P16A20_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A20_2023-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alteración del tiroides últimas 2 semanas</t>
+          <t>Población que ha consumido medicamentos para la alteración del tiroides en las últimas 2 semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,01</t>
+          <t>0,58; 1,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 10,83</t>
+          <t>7,46; 10,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,23</t>
+          <t>4,27; 6,35</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,89</t>
+          <t>0,41; 1,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 9,73</t>
+          <t>6,73; 9,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,1</t>
+          <t>2,89; 5,24</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,97</t>
+          <t>0,44; 2,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 68,46</t>
+          <t>6,72; 63,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 48,03</t>
+          <t>3,95; 43,56</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,83</t>
+          <t>1,1; 3,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,25</t>
+          <t>6,36; 9,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 6,54</t>
+          <t>4,39; 6,49</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,81</t>
+          <t>0,91; 1,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 28,24</t>
+          <t>7,87; 32,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 17,33</t>
+          <t>4,53; 17,53</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alteración del tiroides últimas 2 semanas</t>
+          <t>Población que ha consumido medicamentos para la alteración del tiroides en las últimas 2 semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1979</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1996</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3559; 12750</t>
+          <t>3703; 12011</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1914</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1839</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49702; 73186</t>
+          <t>50392; 74220</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1936</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55199; 81683</t>
+          <t>55991; 83264</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2073</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6215; 22531</t>
+          <t>4930; 22527</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2078</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1950</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64359; 93236</t>
+          <t>64501; 91290</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2074</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2078</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2020</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61044; 109730</t>
+          <t>62219; 112674</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2060</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2060</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2106</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2895; 13881</t>
+          <t>3120; 14840</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1887</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2076</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64101; 638180</t>
+          <t>62638; 593762</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63385; 785675</t>
+          <t>64568; 712524</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1844</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1942</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10072; 35506</t>
+          <t>10184; 34181</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1993</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1990</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70461; 111850</t>
+          <t>69451; 108780</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1908</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 1972</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 1964</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88185; 131910</t>
+          <t>88520; 130973</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30900; 62529</t>
+          <t>31327; 61801</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>288444; 1032918</t>
+          <t>287815; 1179965</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1982</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 1997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>323603; 1233134</t>
+          <t>322547; 1247335</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A20_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A20_2023-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,89</t>
+          <t>0,54; 1,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 10,98</t>
+          <t>7,22; 10,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,35</t>
+          <t>4,22; 6,11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,89</t>
+          <t>0,74; 2,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 9,53</t>
+          <t>6,83; 9,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,24</t>
+          <t>4,0; 5,57</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,11</t>
+          <t>0,4; 1,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,72; 63,7</t>
+          <t>6,62; 10,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 43,56</t>
+          <t>3,78; 5,63</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,69</t>
+          <t>1,1; 3,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,97</t>
+          <t>7,09; 9,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,49</t>
+          <t>4,62; 6,28</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,79</t>
+          <t>0,97; 1,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,87; 32,27</t>
+          <t>7,6; 9,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 17,53</t>
+          <t>4,51; 5,36</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60512</t>
+          <t>64868</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67484</t>
+          <t>72312</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3703; 12011</t>
+          <t>3706; 12706</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50392; 74220</t>
+          <t>52922; 77713</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55991; 83264</t>
+          <t>60028; 87042</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77153</t>
+          <t>86081</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90214</t>
+          <t>99762</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4930; 22527</t>
+          <t>7790; 23389</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64501; 91290</t>
+          <t>73140; 102399</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62219; 112674</t>
+          <t>84710; 118079</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>258882</t>
+          <t>66362</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>265788</t>
+          <t>74318</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3120; 14840</t>
+          <t>3188; 14304</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62638; 593762</t>
+          <t>53665; 82338</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64568; 712524</t>
+          <t>60924; 90769</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>89707</t>
+          <t>93749</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>107891</t>
+          <t>112071</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10184; 34181</t>
+          <t>10849; 33029</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69451; 108780</t>
+          <t>79145; 110369</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88520; 130973</t>
+          <t>97352; 132397</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>47404</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>486253</t>
+          <t>311059</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>531377</t>
+          <t>358463</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31327; 61801</t>
+          <t>34212; 63640</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>287815; 1179965</t>
+          <t>283571; 344144</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>322547; 1247335</t>
+          <t>327281; 389166</t>
         </is>
       </c>
     </row>
